--- a/Team-Data/2012-13/12-16-2012-13.xlsx
+++ b/Team-Data/2012-13/12-16-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -754,7 +821,7 @@
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
         <v>19</v>
@@ -766,7 +833,7 @@
         <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>9</v>
@@ -799,10 +866,10 @@
         <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="n">
         <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>14</v>
       </c>
       <c r="AF3" t="n">
         <v>13</v>
@@ -933,7 +1000,7 @@
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
         <v>10</v>
@@ -957,7 +1024,7 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
         <v>4</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -975,7 +1042,7 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
@@ -984,7 +1051,7 @@
         <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>21</v>
@@ -1124,7 +1191,7 @@
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1136,19 +1203,19 @@
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
         <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>17</v>
@@ -1163,7 +1230,7 @@
         <v>26</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
         <v>5</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH5" t="n">
         <v>6</v>
@@ -1312,10 +1379,10 @@
         <v>19</v>
       </c>
       <c r="AM5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>5</v>
@@ -1324,13 +1391,13 @@
         <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>21</v>
@@ -1345,13 +1412,13 @@
         <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
         <v>7</v>
@@ -1527,10 +1594,10 @@
         <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ6" t="n">
         <v>5</v>
@@ -1542,7 +1609,7 @@
         <v>25</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1719,7 @@
         <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
         <v>30</v>
@@ -1661,7 +1728,7 @@
         <v>29</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>25</v>
@@ -1685,13 +1752,13 @@
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
         <v>26</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="n">
         <v>28</v>
@@ -1703,7 +1770,7 @@
         <v>27</v>
       </c>
       <c r="AV7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1840,7 +1907,7 @@
         <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1855,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="n">
         <v>12</v>
@@ -1867,7 +1934,7 @@
         <v>13</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
         <v>7</v>
@@ -1882,7 +1949,7 @@
         <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV8" t="n">
         <v>25</v>
@@ -1894,7 +1961,7 @@
         <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
         <v>27</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -1935,100 +2002,100 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="J9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.468</v>
+        <v>0.465</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M9" t="n">
         <v>18.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.338</v>
+        <v>0.334</v>
       </c>
       <c r="O9" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T9" t="n">
-        <v>44.9</v>
+        <v>44.6</v>
       </c>
       <c r="U9" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="V9" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y9" t="n">
         <v>6.6</v>
       </c>
-      <c r="Y9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="Z9" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>101.6</v>
+        <v>100.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
         <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
         <v>7</v>
@@ -2043,10 +2110,10 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2055,31 +2122,31 @@
         <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>26</v>
       </c>
-      <c r="AW9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>25</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2088,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -2231,13 +2298,13 @@
         <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS10" t="n">
         <v>15</v>
@@ -2249,7 +2316,7 @@
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2413,13 +2480,13 @@
         <v>18</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2428,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -2481,100 +2548,100 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.478</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="J12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O12" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="P12" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="S12" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T12" t="n">
         <v>44.3</v>
       </c>
       <c r="U12" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Z12" t="n">
         <v>19.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.7</v>
+        <v>104.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ12" t="n">
         <v>4</v>
@@ -2598,10 +2665,10 @@
         <v>4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
         <v>6</v>
@@ -2610,25 +2677,25 @@
         <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>0.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>9</v>
@@ -2774,7 +2841,7 @@
         <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP13" t="n">
         <v>15</v>
@@ -2798,7 +2865,7 @@
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>10</v>
@@ -2965,7 +3032,7 @@
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
         <v>20</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
         <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>0.44</v>
+        <v>0.417</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J15" t="n">
         <v>79.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="O15" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P15" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S15" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T15" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="U15" t="n">
         <v>20.3</v>
@@ -3084,43 +3151,43 @@
         <v>16.2</v>
       </c>
       <c r="W15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.1</v>
+        <v>101.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF15" t="n">
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH15" t="n">
         <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="n">
         <v>27</v>
@@ -3150,7 +3217,7 @@
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
         <v>2</v>
@@ -3162,16 +3229,16 @@
         <v>29</v>
       </c>
       <c r="AW15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3180,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3408,7 @@
         <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3359,7 +3426,7 @@
         <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3551,7 @@
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ17" t="n">
         <v>29</v>
@@ -3502,10 +3569,10 @@
         <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>17</v>
@@ -3526,7 +3593,7 @@
         <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
         <v>26</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3718,10 @@
         <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF18" t="n">
         <v>11</v>
@@ -3678,7 +3745,7 @@
         <v>24</v>
       </c>
       <c r="AM18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
         <v>28</v>
@@ -3702,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV18" t="n">
         <v>4</v>
@@ -3717,7 +3784,7 @@
         <v>4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3903,7 @@
         <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF19" t="n">
         <v>9</v>
@@ -3890,7 +3957,7 @@
         <v>23</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX19" t="n">
         <v>8</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" t="n">
         <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>0.217</v>
+        <v>0.227</v>
       </c>
       <c r="H20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J20" t="n">
         <v>79</v>
@@ -3961,31 +4028,31 @@
         <v>0.441</v>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M20" t="n">
         <v>18.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.401</v>
+        <v>0.394</v>
       </c>
       <c r="O20" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="P20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.778</v>
+        <v>0.78</v>
       </c>
       <c r="R20" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="S20" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T20" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
@@ -3994,37 +4061,37 @@
         <v>14.6</v>
       </c>
       <c r="W20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
         <v>26</v>
       </c>
       <c r="AG20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH20" t="n">
         <v>15</v>
@@ -4036,13 +4103,13 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN20" t="n">
         <v>4</v>
@@ -4057,13 +4124,13 @@
         <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU20" t="n">
         <v>17</v>
@@ -4072,25 +4139,25 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
       </c>
       <c r="BC20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>7.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -4215,7 +4282,7 @@
         <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK21" t="n">
         <v>11</v>
@@ -4230,10 +4297,10 @@
         <v>2</v>
       </c>
       <c r="AO21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ21" t="n">
         <v>16</v>
@@ -4266,7 +4333,7 @@
         <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4430,10 +4497,10 @@
         <v>15</v>
       </c>
       <c r="AU22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -4561,16 +4628,16 @@
         <v>-2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
         <v>20</v>
       </c>
       <c r="AG23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH23" t="n">
         <v>27</v>
@@ -4579,7 +4646,7 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
@@ -4591,7 +4658,7 @@
         <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,13 +4673,13 @@
         <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
       </c>
       <c r="AU23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
@@ -4627,7 +4694,7 @@
         <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -4665,64 +4732,64 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>0.522</v>
       </c>
       <c r="H24" t="n">
         <v>48.4</v>
       </c>
       <c r="I24" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J24" t="n">
         <v>83.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.434</v>
+        <v>0.431</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="M24" t="n">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O24" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="P24" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.732</v>
+        <v>0.736</v>
       </c>
       <c r="R24" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T24" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V24" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="W24" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X24" t="n">
         <v>5.5</v>
@@ -4731,49 +4798,49 @@
         <v>5.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>-2.8</v>
+        <v>-2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" t="n">
         <v>14</v>
       </c>
-      <c r="AF24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
         <v>17</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>18</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>17</v>
       </c>
       <c r="AJ24" t="n">
         <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
         <v>29</v>
@@ -4782,13 +4849,13 @@
         <v>29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR24" t="n">
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
@@ -4800,16 +4867,16 @@
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
@@ -4952,10 +5019,10 @@
         <v>21</v>
       </c>
       <c r="AM25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO25" t="n">
         <v>26</v>
@@ -4967,7 +5034,7 @@
         <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>29</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
         <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>0.478</v>
+        <v>0.455</v>
       </c>
       <c r="H26" t="n">
         <v>49.1</v>
@@ -5047,85 +5114,85 @@
         <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.436</v>
+        <v>0.434</v>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M26" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O26" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="P26" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R26" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S26" t="n">
-        <v>28.3</v>
+        <v>28.6</v>
       </c>
       <c r="T26" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="U26" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="V26" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W26" t="n">
         <v>8.4</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Z26" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AA26" t="n">
         <v>19.8</v>
       </c>
-      <c r="AA26" t="n">
-        <v>19.6</v>
-      </c>
       <c r="AB26" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH26" t="n">
         <v>1</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK26" t="n">
         <v>21</v>
@@ -5134,52 +5201,52 @@
         <v>8</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
       </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX26" t="n">
         <v>20</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB26" t="n">
         <v>14</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>15</v>
       </c>
       <c r="BC26" t="n">
         <v>22</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -5211,91 +5278,91 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E27" t="n">
         <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>0.304</v>
+        <v>0.318</v>
       </c>
       <c r="H27" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="J27" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.429</v>
+        <v>0.434</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
       </c>
       <c r="M27" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="O27" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="R27" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="U27" t="n">
         <v>18.6</v>
       </c>
-      <c r="N27" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="O27" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="P27" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="R27" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="S27" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>41</v>
-      </c>
-      <c r="U27" t="n">
-        <v>18.3</v>
-      </c>
       <c r="V27" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.4</v>
+        <v>-5.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
@@ -5304,46 +5371,46 @@
         <v>15</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
       </c>
       <c r="AM27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN27" t="n">
         <v>19</v>
       </c>
-      <c r="AN27" t="n">
-        <v>25</v>
-      </c>
       <c r="AO27" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AP27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
@@ -5352,19 +5419,19 @@
         <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ27" t="n">
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB27" t="n">
         <v>22</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
@@ -5504,7 +5571,7 @@
         <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
         <v>24</v>
@@ -5531,7 +5598,7 @@
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -5575,70 +5642,70 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
         <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>0.24</v>
+        <v>0.208</v>
       </c>
       <c r="H29" t="n">
         <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J29" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K29" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L29" t="n">
         <v>7.2</v>
       </c>
       <c r="M29" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.328</v>
+        <v>0.332</v>
       </c>
       <c r="O29" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P29" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="R29" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="T29" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U29" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="V29" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="W29" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X29" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Z29" t="n">
         <v>23.7</v>
@@ -5647,13 +5714,13 @@
         <v>19.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>95.5</v>
+        <v>95.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>27</v>
@@ -5662,10 +5729,10 @@
         <v>28</v>
       </c>
       <c r="AG29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
         <v>23</v>
@@ -5683,22 +5750,22 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO29" t="n">
         <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
         <v>23</v>
@@ -5713,22 +5780,22 @@
         <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>13</v>
@@ -5853,7 +5920,7 @@
         <v>12</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>12</v>
@@ -5874,7 +5941,7 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>4</v>
@@ -5889,7 +5956,7 @@
         <v>5</v>
       </c>
       <c r="AV30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
         <v>12</v>
@@ -5910,7 +5977,7 @@
         <v>9</v>
       </c>
       <c r="BC30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-16-2012-13</t>
+          <t>2012-12-16</t>
         </is>
       </c>
     </row>
